--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92568554443</v>
+        <v>46157.93098306771</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93098306771</v>
+        <v>46157.93173419176</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93173419176</v>
+        <v>46157.93400381997</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93400381997</v>
+        <v>46157.93718244931</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93718244931</v>
+        <v>46158.28216575529</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28216575529</v>
+        <v>46158.29681955927</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29681955927</v>
+        <v>46158.29814973386</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29814973386</v>
+        <v>46158.33387636382</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33387636382</v>
+        <v>46158.36857422226</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/11. Отзывы благополучателей/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36857422226</v>
+        <v>46158.37288065715</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
